--- a/DataAnalysis/LF/0.2/Results.xlsx
+++ b/DataAnalysis/LF/0.2/Results.xlsx
@@ -1,27 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B691CEA8-B79E-422C-872E-9BF628567C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="ADV_NOCLSDIV" sheetId="4" r:id="rId2"/>
+    <sheet name="ADV_CLSDIV" sheetId="3" r:id="rId3"/>
+    <sheet name="NOAUG" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+  <si>
+    <t>ERR_i_0</t>
+  </si>
+  <si>
+    <t>ERR_i_1</t>
+  </si>
+  <si>
+    <t>ERR_i_2</t>
+  </si>
+  <si>
+    <t>ERR_i</t>
+  </si>
+  <si>
+    <t>MIN_i</t>
+  </si>
+  <si>
+    <t>CIC_i</t>
+  </si>
+  <si>
+    <t>ERR_0</t>
+  </si>
+  <si>
+    <t>ERR_1</t>
+  </si>
+  <si>
+    <t>ERR_2</t>
+  </si>
+  <si>
+    <t>ERR_0_STD</t>
+  </si>
+  <si>
+    <t>ERR_1_STD</t>
+  </si>
+  <si>
+    <t>ERR_2_STD</t>
+  </si>
+  <si>
+    <t>ERR</t>
+  </si>
+  <si>
+    <t>ERR_STD</t>
+  </si>
+  <si>
+    <t>CIC</t>
+  </si>
+  <si>
+    <t>CIC_STD</t>
+  </si>
+  <si>
+    <t>NOAUG</t>
+  </si>
+  <si>
+    <t>eps=0.1</t>
+  </si>
+  <si>
+    <t>eps=0.01</t>
+  </si>
+  <si>
+    <t>eps=0.001</t>
+  </si>
+  <si>
+    <t>ADV_CLSDIV</t>
+  </si>
+  <si>
+    <t>ADV_NOCLSDIV</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,11 +148,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +430,713 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:T4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66F790C-5674-4FFE-AFAC-55716215CEA8}">
+  <dimension ref="A1:AG10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q3" t="e">
+        <f>AVERAGE(C3:D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R3" t="e">
+        <f>AVERAGE(H3:I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S3" t="e">
+        <f>AVERAGE(M3:N3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" t="e">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U3" t="e">
+        <f>MIN(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V3" t="e">
+        <f>(1/3)*(T3-U3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X3" t="e">
+        <f>AVERAGE(Q3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="e">
+        <f>AVERAGE(R3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="e">
+        <f>AVERAGE(T3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="e">
+        <f>AVERAGE(T3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="e">
+        <f>AVERAGE(V3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q5" t="e">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5:D5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R5" t="e">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5:I5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" t="e">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5:N5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" t="e">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" t="e">
+        <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" t="e">
+        <f t="shared" ref="V5:V10" si="5">(1/3)*(T5-U5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD5" t="e">
+        <f>AVERAGE(T5:T6)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD9" t="e">
+        <f>AVERAGE(T9:T10)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S10" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T10" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FDE21E-9CB3-45CD-ADE0-EE4270AB04E7}">
+  <dimension ref="A1:AG10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q3" t="e">
+        <f>AVERAGE(C3:D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R3" t="e">
+        <f>AVERAGE(H3:I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S3" t="e">
+        <f>AVERAGE(M3:N3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" t="e">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U3" t="e">
+        <f>MIN(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V3" t="e">
+        <f>(1/3)*(T3-U3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X3" t="e">
+        <f>AVERAGE(Q3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD3" t="e">
+        <f>AVERAGE(T3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q5" t="e">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5:D5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R5" t="e">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5:I5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" t="e">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5:N5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" t="e">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" t="e">
+        <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" t="e">
+        <f t="shared" ref="V5:V10" si="5">(1/3)*(T5-U5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X5" t="e">
+        <f>AVERAGE(Q5:Q6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD5" t="e">
+        <f>AVERAGE(T5:T6)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X9" t="e">
+        <f>AVERAGE(Q9:Q10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y9" t="e">
+        <f>_xlfn.STDEV.S(Q9:Q10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z9" t="e">
+        <f>AVERAGE(R9:R10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA9" t="e">
+        <f>_xlfn.STDEV.S(R9:R10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB9" t="e">
+        <f>AVERAGE(S9:S10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC9" t="e">
+        <f>_xlfn.STDEV.S(S9:S10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD9" t="e">
+        <f>AVERAGE(T9:T10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE9" t="e">
+        <f>_xlfn.STDEV.S(T9:T10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF9" t="e">
+        <f>AVERAGE(V9:V10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG9" t="e">
+        <f>_xlfn.STDEV.S(V9:V10)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S10" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T10" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F52E050-0D53-43C0-B5FC-AD6D7416AA3A}">
+  <dimension ref="Q1:AG2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q2" t="e">
+        <f>AVERAGE(C2:D2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R2" t="e">
+        <f>AVERAGE(H2:I2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S2" t="e">
+        <f>AVERAGE(M2:N2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T2" t="e">
+        <f>AVERAGE(Q2:S2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U2" t="e">
+        <f>MIN(Q2:S2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V2" t="e">
+        <f>(1/3)*(T2-U2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>19.5</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>29.5</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataAnalysis/LF/0.2/Results.xlsx
+++ b/DataAnalysis/LF/0.2/Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD71670-270C-4FEA-A38F-783C63EF44AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB03C2E-37E2-4E7F-B1D2-DFDB7325CC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -422,143 +422,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
+      <c r="B2">
+        <v>17.875</v>
+      </c>
+      <c r="C2">
+        <v>3.182497364285509</v>
+      </c>
+      <c r="D2">
+        <v>12.8</v>
+      </c>
       <c r="E2">
-        <v>17.875</v>
+        <v>2.6626065582827887</v>
       </c>
       <c r="F2">
-        <v>3.182497364285509</v>
+        <v>19.975000000000001</v>
       </c>
       <c r="G2">
-        <v>12.8</v>
+        <v>3.2463542304366131</v>
       </c>
       <c r="H2">
-        <v>2.6626065582827887</v>
+        <v>16.883333333333333</v>
       </c>
       <c r="I2">
-        <v>19.975000000000001</v>
+        <v>1.9809767807442635</v>
       </c>
       <c r="J2">
-        <v>3.2463542304366131</v>
+        <v>4.133333333333332</v>
       </c>
       <c r="K2">
-        <v>16.883333333333333</v>
-      </c>
-      <c r="L2">
-        <v>1.9809767807442635</v>
-      </c>
-      <c r="M2">
-        <v>4.133333333333332</v>
-      </c>
-      <c r="N2">
         <v>2.1251762912769978</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
+      <c r="B3">
+        <v>18.3</v>
+      </c>
+      <c r="C3">
+        <v>3.5106979363083899</v>
+      </c>
+      <c r="D3">
+        <v>13.4</v>
+      </c>
       <c r="E3">
-        <v>18.3</v>
+        <v>2.133072900770157</v>
       </c>
       <c r="F3">
-        <v>3.5106979363083899</v>
+        <v>21.4</v>
       </c>
       <c r="G3">
-        <v>13.4</v>
+        <v>2.0124611797498106</v>
       </c>
       <c r="H3">
-        <v>2.133072900770157</v>
+        <v>17.7</v>
       </c>
       <c r="I3">
+        <v>1.9307453943432782</v>
+      </c>
+      <c r="J3">
+        <v>4.2999999999999989</v>
+      </c>
+      <c r="K3">
+        <v>1.6133126720440105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>17.5</v>
+      </c>
+      <c r="C4">
+        <v>2.1505813167606567</v>
+      </c>
+      <c r="D4">
+        <v>12.1</v>
+      </c>
+      <c r="E4">
+        <v>2.6076809620810617</v>
+      </c>
+      <c r="F4">
         <v>21.4</v>
       </c>
-      <c r="J3">
-        <v>2.0124611797498106</v>
-      </c>
-      <c r="K3">
-        <v>17.7</v>
-      </c>
-      <c r="L3">
-        <v>1.9307453943432782</v>
-      </c>
-      <c r="M3">
-        <v>4.2999999999999989</v>
-      </c>
-      <c r="N3">
-        <v>1.6133126720440105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4">
-        <v>17.5</v>
-      </c>
-      <c r="F4">
-        <v>2.1505813167606567</v>
-      </c>
       <c r="G4">
-        <v>12.1</v>
+        <v>5.2009614495783332</v>
       </c>
       <c r="H4">
-        <v>2.6076809620810617</v>
+        <v>17</v>
       </c>
       <c r="I4">
-        <v>21.4</v>
+        <v>2.4008100484813157</v>
       </c>
       <c r="J4">
-        <v>5.2009614495783332</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="K4">
-        <v>17</v>
-      </c>
-      <c r="L4">
-        <v>2.4008100484813157</v>
-      </c>
-      <c r="M4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N4">
         <v>2.4455174412699572</v>
       </c>
     </row>
@@ -767,27 +767,27 @@
         <v>75</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
+        <f t="shared" ref="Q4:Q13" si="0">AVERAGE(C4:D4)</f>
         <v>18.5</v>
       </c>
       <c r="R4">
-        <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
+        <f t="shared" ref="R4:R13" si="1">AVERAGE(H4:I4)</f>
         <v>11</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
+        <f t="shared" ref="S4:S13" si="2">AVERAGE(M4:N4)</f>
         <v>30.5</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
+        <f t="shared" ref="T4:T13" si="3">AVERAGE(Q4:S4)</f>
         <v>20</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
+        <f t="shared" ref="U4:U13" si="4">MIN(Q4:S4)</f>
         <v>11</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4:V14" si="5">T4-U4</f>
+        <f t="shared" ref="V4:V13" si="5">T4-U4</f>
         <v>9</v>
       </c>
     </row>
